--- a/4p-index/STP_Lei-4-2023_Customs-Duties-Law_4P-Index.xlsx
+++ b/4p-index/STP_Lei-4-2023_Customs-Duties-Law_4P-Index.xlsx
@@ -588,57 +588,43 @@
           <t>Raises customs duties on plastic bags (from 20% to 25% of CIF value) and on other plastic products and articles ('demais produtos de plásticos e suas obras', from 10% to 15% of CIF value), as well as on imported bottled mineral water (from 5% to 10%) and on traditional/incandescent lamps (from 20% to 55%), explicitly to discourage their importation on environmental grounds and to protect/incentivise local production of import-substitutable goods (e.g. locally produced mineral water and soap). Simultaneously exempts LED lamps, equipment and raw materials for renewable-energy production, and raw materials for local soap production from customs duties. Per the National Assembly's 2nd Standing Committee report, the law is explicitly grounded in the constitutional objectives of economic development and 'preservação do equilíbrio harmonioso da natureza e do ambiente' (preservation of the harmonious balance of nature and the environment) under Article 10(b)-(c) of the Constitution, and is framed by its sponsors as a step towards 'uma economia verdadeiramente circular' (a genuinely circular economy) in São Tomé and Príncipe. Enacted as part of the broader May-June 2023 fiscal-reform package accompanying the introduction of VAT.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — approved by the National Assembly as Proposta de Lei n.º 05/XII/2.ª/2023 (Government initiative, tabled under Art. 111(f) of the Constitution), reviewed and approved by the 2nd Specialised Standing Committee, and passed in general vote (52 votes in favour) and then — at the request of the ADI parliamentary group under Art. 163 of the Assembly's Rules of Procedure — in a full article-by-article ('na especialidade') vote (Articles 1-3, all approved unanimously) and final global vote (unanimous), per the Diário da Assembleia Nacional, I Série, N.º 4, of 20 May 2023. Published as Lei n.º 4/2023. This is primary legislation, not an executive decree or ministerial order.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>trade/customs, environment, energy, industry, retail/commerce</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -650,25 +636,19 @@
           <t>Art. 1.º ('Agravamento dos direitos aduaneiros' / 'Increase of customs duties') — per the National Assembly's 2nd Specialised Standing Committee report on the underlying bill (Proposta de Lei n.º 05/XII/2.ª/2023): '[o Ponto um do articulado] visa... agravar a importação de produtos de amplo consumo com impacto negativo para o meio ambiente, mormente os sacos de plásticos, que passariam dos 20% actuais para 25% na respectiva taxa.' / '[Point one of the articles] aims... to increase [the duty on] the importation of widely consumed products with a negative environmental impact, notably plastic bags, whose rate would rise from the current 20% to 25%.' NOTE: this reflects the committee report's paraphrase/reported description of Article 1's content, not verbatim statutory text, as the promulgated text itself could not be located (see Column B).</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Authority: the measure is explicitly administered 'ao nível das Alfândegas' / 'at the level of Customs' per the committee report and the Minister of Finance's floor remarks (+0.25). No enforcement sub-score — no specific penalty provision for this rate change was identified in the located material, beyond generic customs-duty collection (0). No monitoring mechanism identified in the located material (0). Unconditional: the new rate is described as a straightforward, generally applicable increase with no stated exemption for this line item (+0.25).</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V2" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -697,57 +677,43 @@
           <t>Raises customs duties on plastic bags (from 20% to 25% of CIF value) and on other plastic products and articles ('demais produtos de plásticos e suas obras', from 10% to 15% of CIF value), as well as on imported bottled mineral water (from 5% to 10%) and on traditional/incandescent lamps (from 20% to 55%), explicitly to discourage their importation on environmental grounds and to protect/incentivise local production of import-substitutable goods (e.g. locally produced mineral water and soap). Simultaneously exempts LED lamps, equipment and raw materials for renewable-energy production, and raw materials for local soap production from customs duties. Per the National Assembly's 2nd Standing Committee report, the law is explicitly grounded in the constitutional objectives of economic development and 'preservação do equilíbrio harmonioso da natureza e do ambiente' (preservation of the harmonious balance of nature and the environment) under Article 10(b)-(c) of the Constitution, and is framed by its sponsors as a step towards 'uma economia verdadeiramente circular' (a genuinely circular economy) in São Tomé and Príncipe. Enacted as part of the broader May-June 2023 fiscal-reform package accompanying the introduction of VAT.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — approved by the National Assembly as Proposta de Lei n.º 05/XII/2.ª/2023 (Government initiative, tabled under Art. 111(f) of the Constitution), reviewed and approved by the 2nd Specialised Standing Committee, and passed in general vote (52 votes in favour) and then — at the request of the ADI parliamentary group under Art. 163 of the Assembly's Rules of Procedure — in a full article-by-article ('na especialidade') vote (Articles 1-3, all approved unanimously) and final global vote (unanimous), per the Diário da Assembleia Nacional, I Série, N.º 4, of 20 May 2023. Published as Lei n.º 4/2023. This is primary legislation, not an executive decree or ministerial order.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>trade/customs, environment, energy, industry, retail/commerce</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="K3" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -759,25 +725,19 @@
           <t>Art. 1.º — per the same committee report: '...demais produtos de plásticos e suas obras, que passariam dos actuais 10%, para 15%.' / '...other plastic products and their manufactures, whose rate would rise from the current 10% to 15%.' This appears to be a distinct tariff line/category from plastic bags (Row 1), covering the broader universe of plastic articles and manufactured goods. NOTE: as with Row 1, this reflects the committee report's paraphrase, not verbatim statutory text (see Column B).</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Authority: administered at the Customs level, as for Row 1 (+0.25). No enforcement sub-score identified (0). No monitoring mechanism identified (0). Unconditional: general rate increase with no stated exemption for this category (+0.25).</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V3" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -806,57 +766,43 @@
           <t>Raises customs duties on plastic bags (from 20% to 25% of CIF value) and on other plastic products and articles ('demais produtos de plásticos e suas obras', from 10% to 15% of CIF value), as well as on imported bottled mineral water (from 5% to 10%) and on traditional/incandescent lamps (from 20% to 55%), explicitly to discourage their importation on environmental grounds and to protect/incentivise local production of import-substitutable goods (e.g. locally produced mineral water and soap). Simultaneously exempts LED lamps, equipment and raw materials for renewable-energy production, and raw materials for local soap production from customs duties. Per the National Assembly's 2nd Standing Committee report, the law is explicitly grounded in the constitutional objectives of economic development and 'preservação do equilíbrio harmonioso da natureza e do ambiente' (preservation of the harmonious balance of nature and the environment) under Article 10(b)-(c) of the Constitution, and is framed by its sponsors as a step towards 'uma economia verdadeiramente circular' (a genuinely circular economy) in São Tomé and Príncipe. Enacted as part of the broader May-June 2023 fiscal-reform package accompanying the introduction of VAT.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — approved by the National Assembly as Proposta de Lei n.º 05/XII/2.ª/2023 (Government initiative, tabled under Art. 111(f) of the Constitution), reviewed and approved by the 2nd Specialised Standing Committee, and passed in general vote (52 votes in favour) and then — at the request of the ADI parliamentary group under Art. 163 of the Assembly's Rules of Procedure — in a full article-by-article ('na especialidade') vote (Articles 1-3, all approved unanimously) and final global vote (unanimous), per the Diário da Assembleia Nacional, I Série, N.º 4, of 20 May 2023. Published as Lei n.º 4/2023. This is primary legislation, not an executive decree or ministerial order.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>trade/customs, environment, energy, industry, retail/commerce</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="K4" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -868,25 +814,19 @@
           <t>Art. 1.º — per the same committee report: '...agravar gradualmente... os direitos aduaneiros inerentes à importação da água mineral, que passaria dos actuais 5% para 10%, na respectiva taxa, visando incentivar o consumo da água mineral produzida localmente.' / '...gradually increase... the customs duties applicable to the importation of mineral water, whose rate would rise from the current 5% to 10%, aiming to incentivise the consumption of locally produced mineral water.'</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Authority: administered at the Customs level, as for Rows 1-2 (+0.25). No enforcement sub-score identified (0). No monitoring mechanism identified (0). Unconditional: general rate increase with no stated exemption (+0.25).</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V4" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
